--- a/upload/acordos_cooperacao_tecnica.xlsx
+++ b/upload/acordos_cooperacao_tecnica.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11100"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="acordos_cooperacao_tecnica" sheetId="1" r:id="rId1"/>
@@ -20758,7 +20758,7 @@
         <v>5152</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>2022</v>
       </c>
@@ -31186,7 +31186,7 @@
         <v>4015</v>
       </c>
     </row>
-    <row r="416" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>2024</v>
       </c>
@@ -31218,7 +31218,7 @@
         <v>4069</v>
       </c>
     </row>
-    <row r="417" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>2024</v>
       </c>
@@ -31250,7 +31250,7 @@
         <v>4072</v>
       </c>
     </row>
-    <row r="418" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>2024</v>
       </c>
@@ -31282,7 +31282,7 @@
         <v>4080</v>
       </c>
     </row>
-    <row r="419" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>2024</v>
       </c>
@@ -34963,7 +34963,7 @@
         <v>46235</v>
       </c>
       <c r="I533" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J533" t="s">
         <v>3553</v>
@@ -34995,7 +34995,7 @@
         <v>46235</v>
       </c>
       <c r="I534" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J534" s="3" t="s">
         <v>2220</v>
@@ -35027,7 +35027,7 @@
         <v>46235</v>
       </c>
       <c r="I535" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J535" s="3" t="s">
         <v>2222</v>
@@ -35059,7 +35059,7 @@
         <v>46235</v>
       </c>
       <c r="I536" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J536" s="3" t="s">
         <v>2231</v>
@@ -35091,7 +35091,7 @@
         <v>46240</v>
       </c>
       <c r="I537" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J537" s="3" t="s">
         <v>2383</v>
@@ -35123,7 +35123,7 @@
         <v>46244</v>
       </c>
       <c r="I538" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J538" s="7" t="s">
         <v>2626</v>
@@ -35155,7 +35155,7 @@
         <v>46258</v>
       </c>
       <c r="I539" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J539" t="s">
         <v>1432</v>
@@ -35187,7 +35187,7 @@
         <v>46259</v>
       </c>
       <c r="I540" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J540" s="3" t="s">
         <v>2383</v>
@@ -35219,7 +35219,7 @@
         <v>46260</v>
       </c>
       <c r="I541" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J541" t="s">
         <v>4737</v>
@@ -35251,7 +35251,7 @@
         <v>46265</v>
       </c>
       <c r="I542" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J542" t="s">
         <v>355</v>
@@ -35481,7 +35481,7 @@
         <v>3435</v>
       </c>
     </row>
-    <row r="550" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A550" s="12">
         <v>2022</v>
       </c>
@@ -36505,7 +36505,7 @@
         <v>5422</v>
       </c>
     </row>
-    <row r="582" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A582" s="12">
         <v>2021</v>
       </c>
@@ -42164,7 +42164,7 @@
         <v>3950</v>
       </c>
     </row>
-    <row r="758" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A758">
         <v>2025</v>
       </c>
@@ -45243,7 +45243,7 @@
         <v>3887</v>
       </c>
     </row>
-    <row r="854" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A854" s="12">
         <v>2022</v>
       </c>
@@ -46203,7 +46203,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="884" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A884">
         <v>2022</v>
       </c>
@@ -46235,7 +46235,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="885" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A885">
         <v>2022</v>
       </c>
@@ -46270,7 +46270,7 @@
         <v>50603666</v>
       </c>
     </row>
-    <row r="886" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A886">
         <v>2025</v>
       </c>
@@ -48772,7 +48772,7 @@
         <v>5330</v>
       </c>
     </row>
-    <row r="964" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A964">
         <v>2024</v>
       </c>
@@ -50954,7 +50954,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="1032" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1032" s="12">
         <v>2022</v>
       </c>
@@ -52781,7 +52781,7 @@
         <v>4950</v>
       </c>
     </row>
-    <row r="1089" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1089" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1089" s="12">
         <v>2023</v>
       </c>
@@ -58346,7 +58346,7 @@
         <v>2248</v>
       </c>
     </row>
-    <row r="1263" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1263" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1263" s="12">
         <v>2023</v>
       </c>
@@ -59987,7 +59987,7 @@
         <v>3482</v>
       </c>
     </row>
-    <row r="1314" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1314" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1314">
         <v>2026</v>
       </c>
@@ -60019,7 +60019,7 @@
         <v>3474</v>
       </c>
     </row>
-    <row r="1315" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1315" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1315">
         <v>2025</v>
       </c>
@@ -61971,7 +61971,7 @@
         <v>3056</v>
       </c>
     </row>
-    <row r="1376" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1376" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1376" s="12">
         <v>2024</v>
       </c>
@@ -65375,7 +65375,7 @@
         <v>4199</v>
       </c>
     </row>
-    <row r="1482" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1482" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1482" s="12">
         <v>2024</v>
       </c>
@@ -65919,7 +65919,7 @@
         <v>2677</v>
       </c>
     </row>
-    <row r="1499" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1499" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1499" s="12">
         <v>2024</v>
       </c>
@@ -67720,7 +67720,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="1555" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1555" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1555">
         <v>2024</v>
       </c>
@@ -67752,7 +67752,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="1556" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1556" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1556">
         <v>2024</v>
       </c>
@@ -67784,7 +67784,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="1557" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1557" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1557">
         <v>2024</v>
       </c>
@@ -69416,7 +69416,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="1608" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1608" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1608" s="12">
         <v>2025</v>
       </c>
@@ -69480,7 +69480,7 @@
         <v>3464</v>
       </c>
     </row>
-    <row r="1610" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1610" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1610" s="12">
         <v>2025</v>
       </c>
@@ -69928,7 +69928,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="1624" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1624" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A1624">
         <v>2021</v>
       </c>
@@ -70315,7 +70315,7 @@
         <v>51132511</v>
       </c>
     </row>
-    <row r="1636" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1636" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1636" s="12">
         <v>2025</v>
       </c>
@@ -73640,7 +73640,7 @@
         <v>2964</v>
       </c>
     </row>
-    <row r="1740" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1740" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1740">
         <v>2025</v>
       </c>
@@ -73672,7 +73672,7 @@
         <v>3466</v>
       </c>
     </row>
-    <row r="1741" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1741" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1741">
         <v>2025</v>
       </c>
@@ -74021,7 +74021,7 @@
         <v>3061</v>
       </c>
     </row>
-    <row r="1752" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="1752" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1752">
         <v>2025</v>
       </c>
@@ -76069,7 +76069,7 @@
         <v>3012</v>
       </c>
     </row>
-    <row r="1816" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1816" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1816" s="12">
         <v>2026</v>
       </c>
@@ -76613,7 +76613,7 @@
         <v>5203</v>
       </c>
     </row>
-    <row r="1833" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1833" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1833" s="12">
         <v>2026</v>
       </c>
@@ -77253,7 +77253,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="1853" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1853" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1853" s="12">
         <v>2025</v>
       </c>
@@ -77605,7 +77605,7 @@
         <v>3192</v>
       </c>
     </row>
-    <row r="1864" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1864" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1864">
         <v>2023</v>
       </c>
@@ -77637,7 +77637,7 @@
         <v>2675</v>
       </c>
     </row>
-    <row r="1865" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1865" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1865">
         <v>2023</v>
       </c>
@@ -77669,7 +77669,7 @@
         <v>4408</v>
       </c>
     </row>
-    <row r="1866" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1866" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1866">
         <v>2022</v>
       </c>
@@ -77733,7 +77733,7 @@
         <v>3183</v>
       </c>
     </row>
-    <row r="1868" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1868" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1868" s="12">
         <v>2015</v>
       </c>
@@ -77765,7 +77765,7 @@
         <v>4579</v>
       </c>
     </row>
-    <row r="1869" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1869" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1869" s="12">
         <v>2015</v>
       </c>
@@ -77797,7 +77797,7 @@
         <v>4595</v>
       </c>
     </row>
-    <row r="1870" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1870" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1870" s="12">
         <v>2015</v>
       </c>
@@ -77829,7 +77829,7 @@
         <v>4626</v>
       </c>
     </row>
-    <row r="1871" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1871" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1871" s="6">
         <v>2014</v>
       </c>
@@ -77861,7 +77861,7 @@
         <v>2636</v>
       </c>
     </row>
-    <row r="1872" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1872" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1872" s="12">
         <v>2014</v>
       </c>
